--- a/jyx2/Assets/Mods/jshyl/Configs/战斗.xlsx
+++ b/jyx2/Assets/Mods/jshyl/Configs/战斗.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="252">
   <si>
     <t>编号</t>
   </si>
@@ -985,6 +985,21 @@
   <si>
     <t>0,1</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>越女剑初遇</t>
+  </si>
+  <si>
+    <t>Jyx2Battle_5</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>301|302</t>
   </si>
 </sst>
 </file>
@@ -1323,16 +1338,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H144"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H145"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" ns3:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="24.6328125" customWidth="1"/>
     <col min="6" max="6" width="9.1796875" customWidth="1"/>
     <col min="8" max="8" width="91" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ns3:dyDescent="0.25">
       <c r="A1" t="s">
         <v>237</v>
       </c>
@@ -1340,7 +1355,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="13" ns3:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1366,7 +1381,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="13" ns3:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>238</v>
       </c>
@@ -1392,7 +1407,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ns3:dyDescent="0.25">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -1418,7 +1433,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ns3:dyDescent="0.25">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1444,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ns3:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1470,7 +1485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ns3:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1496,7 +1511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ns3:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1522,7 +1537,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ns3:dyDescent="0.25">
       <c r="A9">
         <v>4</v>
       </c>
@@ -1548,7 +1563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="13" ns3:dyDescent="0.25">
       <c r="A10">
         <v>5</v>
       </c>
@@ -1574,7 +1589,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ns3:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
@@ -1600,7 +1615,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ns3:dyDescent="0.25">
       <c r="A12">
         <v>7</v>
       </c>
@@ -1626,7 +1641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ns3:dyDescent="0.25">
       <c r="A13">
         <v>8</v>
       </c>
@@ -1652,7 +1667,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ns3:dyDescent="0.25">
       <c r="A14">
         <v>9</v>
       </c>
@@ -1678,7 +1693,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ns3:dyDescent="0.25">
       <c r="A15">
         <v>10</v>
       </c>
@@ -1704,7 +1719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ns3:dyDescent="0.25">
       <c r="A16">
         <v>11</v>
       </c>
@@ -1730,7 +1745,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ns3:dyDescent="0.25">
       <c r="A17">
         <v>12</v>
       </c>
@@ -1756,7 +1771,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ns3:dyDescent="0.25">
       <c r="A18">
         <v>13</v>
       </c>
@@ -1782,7 +1797,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ns3:dyDescent="0.25">
       <c r="A19">
         <v>14</v>
       </c>
@@ -1808,7 +1823,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ns3:dyDescent="0.25">
       <c r="A20">
         <v>15</v>
       </c>
@@ -1834,7 +1849,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ns3:dyDescent="0.25">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1860,7 +1875,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ns3:dyDescent="0.25">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1886,7 +1901,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ns3:dyDescent="0.25">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1912,7 +1927,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ns3:dyDescent="0.25">
       <c r="A24">
         <v>19</v>
       </c>
@@ -1938,7 +1953,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ns3:dyDescent="0.25">
       <c r="A25">
         <v>20</v>
       </c>
@@ -1964,7 +1979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ns3:dyDescent="0.25">
       <c r="A26">
         <v>21</v>
       </c>
@@ -1990,7 +2005,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ns3:dyDescent="0.25">
       <c r="A27">
         <v>22</v>
       </c>
@@ -2016,7 +2031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ns3:dyDescent="0.25">
       <c r="A28">
         <v>23</v>
       </c>
@@ -2042,7 +2057,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ns3:dyDescent="0.25">
       <c r="A29">
         <v>24</v>
       </c>
@@ -2068,7 +2083,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ns3:dyDescent="0.25">
       <c r="A30">
         <v>25</v>
       </c>
@@ -2094,7 +2109,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ns3:dyDescent="0.25">
       <c r="A31">
         <v>26</v>
       </c>
@@ -2120,7 +2135,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ns3:dyDescent="0.25">
       <c r="A32">
         <v>27</v>
       </c>
@@ -2146,7 +2161,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ns3:dyDescent="0.25">
       <c r="A33">
         <v>28</v>
       </c>
@@ -2172,7 +2187,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ns3:dyDescent="0.25">
       <c r="A34">
         <v>29</v>
       </c>
@@ -2198,7 +2213,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ns3:dyDescent="0.25">
       <c r="A35">
         <v>30</v>
       </c>
@@ -2224,7 +2239,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ns3:dyDescent="0.25">
       <c r="A36">
         <v>31</v>
       </c>
@@ -2250,7 +2265,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ns3:dyDescent="0.25">
       <c r="A37">
         <v>32</v>
       </c>
@@ -2276,7 +2291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ns3:dyDescent="0.25">
       <c r="A38">
         <v>33</v>
       </c>
@@ -2302,7 +2317,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ns3:dyDescent="0.25">
       <c r="A39">
         <v>34</v>
       </c>
@@ -2328,7 +2343,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ns3:dyDescent="0.25">
       <c r="A40">
         <v>35</v>
       </c>
@@ -2354,7 +2369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ns3:dyDescent="0.25">
       <c r="A41">
         <v>36</v>
       </c>
@@ -2380,7 +2395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ns3:dyDescent="0.25">
       <c r="A42">
         <v>37</v>
       </c>
@@ -2406,7 +2421,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ns3:dyDescent="0.25">
       <c r="A43">
         <v>38</v>
       </c>
@@ -2432,7 +2447,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ns3:dyDescent="0.25">
       <c r="A44">
         <v>39</v>
       </c>
@@ -2458,7 +2473,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ns3:dyDescent="0.25">
       <c r="A45">
         <v>40</v>
       </c>
@@ -2484,7 +2499,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ns3:dyDescent="0.25">
       <c r="A46">
         <v>41</v>
       </c>
@@ -2510,7 +2525,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ns3:dyDescent="0.25">
       <c r="A47">
         <v>42</v>
       </c>
@@ -2536,7 +2551,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ns3:dyDescent="0.25">
       <c r="A48">
         <v>43</v>
       </c>
@@ -2562,7 +2577,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ns3:dyDescent="0.25">
       <c r="A49">
         <v>44</v>
       </c>
@@ -2588,7 +2603,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ns3:dyDescent="0.25">
       <c r="A50">
         <v>45</v>
       </c>
@@ -2614,7 +2629,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ns3:dyDescent="0.25">
       <c r="A51">
         <v>46</v>
       </c>
@@ -2640,7 +2655,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ns3:dyDescent="0.25">
       <c r="A52">
         <v>47</v>
       </c>
@@ -2666,7 +2681,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ns3:dyDescent="0.25">
       <c r="A53">
         <v>48</v>
       </c>
@@ -2692,7 +2707,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ns3:dyDescent="0.25">
       <c r="A54">
         <v>49</v>
       </c>
@@ -2718,7 +2733,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ns3:dyDescent="0.25">
       <c r="A55">
         <v>50</v>
       </c>
@@ -2744,7 +2759,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ns3:dyDescent="0.25">
       <c r="A56">
         <v>51</v>
       </c>
@@ -2770,7 +2785,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ns3:dyDescent="0.25">
       <c r="A57">
         <v>52</v>
       </c>
@@ -2796,7 +2811,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ns3:dyDescent="0.25">
       <c r="A58">
         <v>53</v>
       </c>
@@ -2822,7 +2837,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ns3:dyDescent="0.25">
       <c r="A59">
         <v>54</v>
       </c>
@@ -2848,7 +2863,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ns3:dyDescent="0.25">
       <c r="A60">
         <v>55</v>
       </c>
@@ -2874,7 +2889,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ns3:dyDescent="0.25">
       <c r="A61">
         <v>56</v>
       </c>
@@ -2900,7 +2915,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ns3:dyDescent="0.25">
       <c r="A62">
         <v>57</v>
       </c>
@@ -2926,7 +2941,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ns3:dyDescent="0.25">
       <c r="A63">
         <v>58</v>
       </c>
@@ -2952,7 +2967,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ns3:dyDescent="0.25">
       <c r="A64">
         <v>59</v>
       </c>
@@ -2978,7 +2993,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ns3:dyDescent="0.25">
       <c r="A65">
         <v>60</v>
       </c>
@@ -3004,7 +3019,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ns3:dyDescent="0.25">
       <c r="A66">
         <v>61</v>
       </c>
@@ -3030,7 +3045,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ns3:dyDescent="0.25">
       <c r="A67">
         <v>62</v>
       </c>
@@ -3056,7 +3071,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ns3:dyDescent="0.25">
       <c r="A68">
         <v>63</v>
       </c>
@@ -3082,7 +3097,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ns3:dyDescent="0.25">
       <c r="A69">
         <v>64</v>
       </c>
@@ -3108,7 +3123,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ns3:dyDescent="0.25">
       <c r="A70">
         <v>65</v>
       </c>
@@ -3134,7 +3149,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ns3:dyDescent="0.25">
       <c r="A71">
         <v>66</v>
       </c>
@@ -3160,7 +3175,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ns3:dyDescent="0.25">
       <c r="A72">
         <v>67</v>
       </c>
@@ -3186,7 +3201,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ns3:dyDescent="0.25">
       <c r="A73">
         <v>68</v>
       </c>
@@ -3212,7 +3227,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ns3:dyDescent="0.25">
       <c r="A74">
         <v>69</v>
       </c>
@@ -3238,7 +3253,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ns3:dyDescent="0.25">
       <c r="A75">
         <v>70</v>
       </c>
@@ -3264,7 +3279,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ns3:dyDescent="0.25">
       <c r="A76">
         <v>71</v>
       </c>
@@ -3290,7 +3305,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ns3:dyDescent="0.25">
       <c r="A77">
         <v>72</v>
       </c>
@@ -3316,7 +3331,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ns3:dyDescent="0.25">
       <c r="A78">
         <v>73</v>
       </c>
@@ -3342,7 +3357,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ns3:dyDescent="0.25">
       <c r="A79">
         <v>74</v>
       </c>
@@ -3368,7 +3383,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ns3:dyDescent="0.25">
       <c r="A80">
         <v>75</v>
       </c>
@@ -3394,7 +3409,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ns3:dyDescent="0.25">
       <c r="A81">
         <v>76</v>
       </c>
@@ -3420,7 +3435,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ns3:dyDescent="0.25">
       <c r="A82">
         <v>77</v>
       </c>
@@ -3446,7 +3461,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="13" ns3:dyDescent="0.25">
       <c r="A83">
         <v>78</v>
       </c>
@@ -3472,7 +3487,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ns3:dyDescent="0.25">
       <c r="A84">
         <v>79</v>
       </c>
@@ -3498,7 +3513,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ns3:dyDescent="0.25">
       <c r="A85">
         <v>80</v>
       </c>
@@ -3524,7 +3539,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ns3:dyDescent="0.25">
       <c r="A86">
         <v>81</v>
       </c>
@@ -3550,7 +3565,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ns3:dyDescent="0.25">
       <c r="A87">
         <v>82</v>
       </c>
@@ -3576,7 +3591,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ns3:dyDescent="0.25">
       <c r="A88">
         <v>83</v>
       </c>
@@ -3602,7 +3617,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ns3:dyDescent="0.25">
       <c r="A89">
         <v>84</v>
       </c>
@@ -3628,7 +3643,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ns3:dyDescent="0.25">
       <c r="A90">
         <v>85</v>
       </c>
@@ -3654,7 +3669,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ns3:dyDescent="0.25">
       <c r="A91">
         <v>86</v>
       </c>
@@ -3680,7 +3695,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ns3:dyDescent="0.25">
       <c r="A92">
         <v>87</v>
       </c>
@@ -3706,7 +3721,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ns3:dyDescent="0.25">
       <c r="A93">
         <v>88</v>
       </c>
@@ -3732,7 +3747,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ns3:dyDescent="0.25">
       <c r="A94">
         <v>89</v>
       </c>
@@ -3758,7 +3773,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ns3:dyDescent="0.25">
       <c r="A95">
         <v>90</v>
       </c>
@@ -3784,7 +3799,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ns3:dyDescent="0.25">
       <c r="A96">
         <v>91</v>
       </c>
@@ -3810,7 +3825,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ns3:dyDescent="0.25">
       <c r="A97">
         <v>92</v>
       </c>
@@ -3836,7 +3851,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ns3:dyDescent="0.25">
       <c r="A98">
         <v>93</v>
       </c>
@@ -3862,7 +3877,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ns3:dyDescent="0.25">
       <c r="A99">
         <v>94</v>
       </c>
@@ -3888,7 +3903,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ns3:dyDescent="0.25">
       <c r="A100">
         <v>95</v>
       </c>
@@ -3914,7 +3929,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ns3:dyDescent="0.25">
       <c r="A101">
         <v>96</v>
       </c>
@@ -3940,7 +3955,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ns3:dyDescent="0.25">
       <c r="A102">
         <v>97</v>
       </c>
@@ -3966,7 +3981,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ns3:dyDescent="0.25">
       <c r="A103">
         <v>98</v>
       </c>
@@ -3992,7 +4007,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ns3:dyDescent="0.25">
       <c r="A104">
         <v>99</v>
       </c>
@@ -4018,7 +4033,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" ns3:dyDescent="0.25">
       <c r="A105">
         <v>100</v>
       </c>
@@ -4044,7 +4059,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ns3:dyDescent="0.25">
       <c r="A106">
         <v>101</v>
       </c>
@@ -4070,7 +4085,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ns3:dyDescent="0.25">
       <c r="A107">
         <v>102</v>
       </c>
@@ -4096,7 +4111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ns3:dyDescent="0.25">
       <c r="A108">
         <v>103</v>
       </c>
@@ -4122,7 +4137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ns3:dyDescent="0.25">
       <c r="A109">
         <v>104</v>
       </c>
@@ -4148,7 +4163,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ns3:dyDescent="0.25">
       <c r="A110">
         <v>105</v>
       </c>
@@ -4174,7 +4189,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ns3:dyDescent="0.25">
       <c r="A111">
         <v>106</v>
       </c>
@@ -4200,7 +4215,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ns3:dyDescent="0.25">
       <c r="A112">
         <v>107</v>
       </c>
@@ -4226,7 +4241,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ns3:dyDescent="0.25">
       <c r="A113">
         <v>108</v>
       </c>
@@ -4252,7 +4267,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ns3:dyDescent="0.25">
       <c r="A114">
         <v>109</v>
       </c>
@@ -4278,7 +4293,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" ns3:dyDescent="0.25">
       <c r="A115">
         <v>110</v>
       </c>
@@ -4304,7 +4319,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ns3:dyDescent="0.25">
       <c r="A116">
         <v>111</v>
       </c>
@@ -4330,7 +4345,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" ns3:dyDescent="0.25">
       <c r="A117">
         <v>112</v>
       </c>
@@ -4356,7 +4371,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ns3:dyDescent="0.25">
       <c r="A118">
         <v>113</v>
       </c>
@@ -4382,7 +4397,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ns3:dyDescent="0.25">
       <c r="A119">
         <v>114</v>
       </c>
@@ -4408,7 +4423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ns3:dyDescent="0.25">
       <c r="A120">
         <v>115</v>
       </c>
@@ -4434,7 +4449,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ns3:dyDescent="0.25">
       <c r="A121">
         <v>116</v>
       </c>
@@ -4460,7 +4475,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ns3:dyDescent="0.25">
       <c r="A122">
         <v>117</v>
       </c>
@@ -4486,7 +4501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ns3:dyDescent="0.25">
       <c r="A123">
         <v>118</v>
       </c>
@@ -4512,7 +4527,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ns3:dyDescent="0.25">
       <c r="A124">
         <v>119</v>
       </c>
@@ -4538,7 +4553,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ns3:dyDescent="0.25">
       <c r="A125">
         <v>120</v>
       </c>
@@ -4564,7 +4579,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" ns3:dyDescent="0.25">
       <c r="A126">
         <v>121</v>
       </c>
@@ -4590,7 +4605,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ns3:dyDescent="0.25">
       <c r="A127">
         <v>122</v>
       </c>
@@ -4616,7 +4631,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ns3:dyDescent="0.25">
       <c r="A128">
         <v>123</v>
       </c>
@@ -4642,7 +4657,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" ns3:dyDescent="0.25">
       <c r="A129">
         <v>124</v>
       </c>
@@ -4668,7 +4683,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ns3:dyDescent="0.25">
       <c r="A130">
         <v>125</v>
       </c>
@@ -4694,7 +4709,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ns3:dyDescent="0.25">
       <c r="A131">
         <v>126</v>
       </c>
@@ -4720,7 +4735,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ns3:dyDescent="0.25">
       <c r="A132">
         <v>127</v>
       </c>
@@ -4746,7 +4761,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ns3:dyDescent="0.25">
       <c r="A133">
         <v>128</v>
       </c>
@@ -4772,7 +4787,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ns3:dyDescent="0.25">
       <c r="A134">
         <v>129</v>
       </c>
@@ -4798,7 +4813,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ns3:dyDescent="0.25">
       <c r="A135">
         <v>130</v>
       </c>
@@ -4824,7 +4839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ns3:dyDescent="0.25">
       <c r="A136">
         <v>131</v>
       </c>
@@ -4850,7 +4865,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ns3:dyDescent="0.25">
       <c r="A137">
         <v>132</v>
       </c>
@@ -4876,7 +4891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ns3:dyDescent="0.25">
       <c r="A138">
         <v>133</v>
       </c>
@@ -4902,7 +4917,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ns3:dyDescent="0.25">
       <c r="A139">
         <v>134</v>
       </c>
@@ -4928,7 +4943,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ns3:dyDescent="0.25">
       <c r="A140">
         <v>135</v>
       </c>
@@ -4954,7 +4969,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ns3:dyDescent="0.25">
       <c r="A141">
         <v>136</v>
       </c>
@@ -4980,7 +4995,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ns3:dyDescent="0.25">
       <c r="A142">
         <v>137</v>
       </c>
@@ -5006,7 +5021,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ns3:dyDescent="0.25">
       <c r="A143">
         <v>138</v>
       </c>
@@ -5032,7 +5047,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" ns3:dyDescent="0.25">
       <c r="A144">
         <v>139</v>
       </c>
@@ -5056,12 +5071,38 @@
       </c>
       <c r="H144" s="2" t="s">
         <v>245</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ns3:dyDescent="0.25">
+      <c r="A145">
+        <v>140</v>
+      </c>
+      <c r="B145" t="s">
+        <v>247</v>
+      </c>
+      <c r="C145" t="s">
+        <v>248</v>
+      </c>
+      <c r="D145">
+        <v>300</v>
+      </c>
+      <c r="E145">
+        <v>5</v>
+      </c>
+      <c r="F145">
+        <v>320</v>
+      </c>
+      <c r="G145">
+        <v>-1</v>
+      </c>
+      <c r="H145" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
 </worksheet>
 </file>